--- a/test/standard_mapping/input_dpr_first100.xlsx
+++ b/test/standard_mapping/input_dpr_first100.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Program\VScode\workspace\data-governance\test\standard_mapping\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\vscode\data-governance\test\standard_mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383D714B-26B8-4C33-991A-A798C5C68DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF58682-DB4A-4E80-9A6C-3A5C4E20A2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10650" yWindow="3975" windowWidth="28800" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1021,7 +1021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1068,6 +1068,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1372,31 +1375,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z378"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="4.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.75" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="5.77734375" customWidth="1"/>
-    <col min="5" max="5" width="4.88671875" customWidth="1"/>
+    <col min="4" max="4" width="5.75" customWidth="1"/>
+    <col min="5" max="5" width="4.875" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="3.6640625" customWidth="1"/>
-    <col min="8" max="8" width="5.44140625" customWidth="1"/>
-    <col min="9" max="9" width="4.109375" customWidth="1"/>
+    <col min="7" max="7" width="3.625" customWidth="1"/>
+    <col min="8" max="8" width="5.5" customWidth="1"/>
+    <col min="9" max="9" width="4.125" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" customWidth="1"/>
-    <col min="12" max="12" width="4.44140625" customWidth="1"/>
-    <col min="13" max="13" width="6.109375" customWidth="1"/>
-    <col min="14" max="14" width="5.109375" customWidth="1"/>
-    <col min="15" max="15" width="14.88671875" customWidth="1"/>
+    <col min="11" max="11" width="5.625" customWidth="1"/>
+    <col min="12" max="12" width="4.5" customWidth="1"/>
+    <col min="13" max="13" width="6.125" customWidth="1"/>
+    <col min="14" max="14" width="5.125" customWidth="1"/>
+    <col min="15" max="15" width="14.875" customWidth="1"/>
     <col min="17" max="17" width="24" style="5" customWidth="1"/>
-    <col min="18" max="18" width="11.77734375" customWidth="1"/>
+    <col min="18" max="18" width="11.75" customWidth="1"/>
     <col min="19" max="19" width="0" hidden="1"/>
-    <col min="20" max="20" width="5.33203125" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="5.375" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="0" hidden="1"/>
-    <col min="23" max="23" width="36.109375" customWidth="1"/>
-    <col min="25" max="25" width="36.33203125" customWidth="1"/>
-    <col min="26" max="26" width="16.44140625" customWidth="1"/>
+    <col min="23" max="23" width="36.125" customWidth="1"/>
+    <col min="25" max="25" width="36.375" customWidth="1"/>
+    <col min="26" max="26" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -2568,243 +2571,243 @@
         <v>171</v>
       </c>
     </row>
-    <row r="47" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J47" s="12" t="s">
+    <row r="47" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J47" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O47" s="12" t="s">
+      <c r="O47" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="P47" s="12" t="s">
+      <c r="P47" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="Q47" s="12" t="s">
+      <c r="Q47" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="R47" s="12" t="s">
+      <c r="R47" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V47" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W47" s="12"/>
-      <c r="Y47" s="12" t="s">
+      <c r="V47" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W47" s="19"/>
+      <c r="Y47" s="19" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J48" s="12" t="s">
+    <row r="48" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J48" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O48" s="12" t="s">
+      <c r="O48" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="P48" s="12" t="s">
+      <c r="P48" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="Q48" s="12" t="s">
+      <c r="Q48" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="R48" s="12" t="s">
+      <c r="R48" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V48" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W48" s="12"/>
-      <c r="Y48" s="12" t="s">
+      <c r="V48" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W48" s="19"/>
+      <c r="Y48" s="19" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J49" s="12" t="s">
+    <row r="49" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J49" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O49" s="12" t="s">
+      <c r="O49" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="P49" s="12" t="s">
+      <c r="P49" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="Q49" s="12" t="s">
+      <c r="Q49" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="R49" s="12" t="s">
+      <c r="R49" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V49" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W49" s="12"/>
-      <c r="Y49" s="12" t="s">
+      <c r="V49" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W49" s="19"/>
+      <c r="Y49" s="19" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J50" s="12" t="s">
+    <row r="50" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J50" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O50" s="12" t="s">
+      <c r="O50" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="P50" s="12" t="s">
+      <c r="P50" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="Q50" s="12" t="s">
+      <c r="Q50" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="R50" s="12" t="s">
+      <c r="R50" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V50" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W50" s="12"/>
-      <c r="Y50" s="12" t="s">
+      <c r="V50" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W50" s="19"/>
+      <c r="Y50" s="19" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J51" s="12" t="s">
+    <row r="51" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J51" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O51" s="12" t="s">
+      <c r="O51" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="P51" s="12" t="s">
+      <c r="P51" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="Q51" s="12" t="s">
+      <c r="Q51" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="R51" s="12" t="s">
+      <c r="R51" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V51" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W51" s="12"/>
-      <c r="Y51" s="12" t="s">
+      <c r="V51" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W51" s="19"/>
+      <c r="Y51" s="19" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="52" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J52" s="12" t="s">
+    <row r="52" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J52" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O52" s="12" t="s">
+      <c r="O52" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="P52" s="12" t="s">
+      <c r="P52" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="Q52" s="12" t="s">
+      <c r="Q52" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="R52" s="12" t="s">
+      <c r="R52" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V52" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W52" s="12"/>
-      <c r="Y52" s="12" t="s">
+      <c r="V52" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W52" s="19"/>
+      <c r="Y52" s="19" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="53" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J53" s="12" t="s">
+    <row r="53" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J53" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O53" s="12" t="s">
+      <c r="O53" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="P53" s="12" t="s">
+      <c r="P53" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="Q53" s="12" t="s">
+      <c r="Q53" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="R53" s="12" t="s">
+      <c r="R53" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V53" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W53" s="12"/>
-      <c r="Y53" s="12" t="s">
+      <c r="V53" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W53" s="19"/>
+      <c r="Y53" s="19" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J54" s="12" t="s">
+    <row r="54" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J54" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O54" s="12" t="s">
+      <c r="O54" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="P54" s="12" t="s">
+      <c r="P54" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="Q54" s="12" t="s">
+      <c r="Q54" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="R54" s="12" t="s">
+      <c r="R54" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V54" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W54" s="12"/>
-      <c r="Y54" s="12" t="s">
+      <c r="V54" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W54" s="19"/>
+      <c r="Y54" s="19" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J55" s="12" t="s">
+    <row r="55" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J55" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O55" s="12" t="s">
+      <c r="O55" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="P55" s="12" t="s">
+      <c r="P55" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="Q55" s="12" t="s">
+      <c r="Q55" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="R55" s="12" t="s">
+      <c r="R55" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V55" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W55" s="12"/>
-      <c r="Y55" s="12" t="s">
+      <c r="V55" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W55" s="19"/>
+      <c r="Y55" s="19" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="10:25" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="J56" s="12" t="s">
+    <row r="56" spans="10:25" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="J56" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="O56" s="12" t="s">
+      <c r="O56" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="P56" s="12" t="s">
+      <c r="P56" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="Q56" s="12" t="s">
+      <c r="Q56" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="R56" s="12" t="s">
+      <c r="R56" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="V56" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W56" s="12"/>
-      <c r="Y56" s="12" t="s">
+      <c r="V56" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="W56" s="19"/>
+      <c r="Y56" s="19" t="s">
         <v>193</v>
       </c>
     </row>
@@ -3805,7 +3808,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="98" spans="10:25" ht="28.8" customHeight="1">
+    <row r="98" spans="10:25" ht="28.9" customHeight="1">
       <c r="J98" s="2" t="s">
         <v>280</v>
       </c>
@@ -3935,7 +3938,7 @@
     <row r="112" spans="10:25" ht="15" customHeight="1"/>
     <row r="113" ht="15" customHeight="1"/>
     <row r="114" s="9" customFormat="1" ht="15" customHeight="1"/>
-    <row r="115" ht="28.8" customHeight="1"/>
+    <row r="115" ht="28.9" customHeight="1"/>
     <row r="116" ht="30" customHeight="1"/>
     <row r="117" ht="15" customHeight="1"/>
     <row r="118" ht="15" customHeight="1"/>
@@ -4055,17 +4058,17 @@
     <row r="232" ht="30" customHeight="1"/>
     <row r="233" ht="30" customHeight="1"/>
     <row r="234" ht="30" customHeight="1"/>
-    <row r="237" ht="28.8" customHeight="1"/>
-    <row r="239" ht="28.8" customHeight="1"/>
-    <row r="240" ht="28.8" customHeight="1"/>
-    <row r="241" ht="28.8" customHeight="1"/>
-    <row r="244" ht="28.8" customHeight="1"/>
-    <row r="245" ht="28.8" customHeight="1"/>
-    <row r="246" ht="28.8" customHeight="1"/>
-    <row r="248" ht="28.8" customHeight="1"/>
-    <row r="249" ht="28.8" customHeight="1"/>
-    <row r="250" ht="28.8" customHeight="1"/>
-    <row r="251" ht="28.8" customHeight="1"/>
+    <row r="237" ht="28.9" customHeight="1"/>
+    <row r="239" ht="28.9" customHeight="1"/>
+    <row r="240" ht="28.9" customHeight="1"/>
+    <row r="241" ht="28.9" customHeight="1"/>
+    <row r="244" ht="28.9" customHeight="1"/>
+    <row r="245" ht="28.9" customHeight="1"/>
+    <row r="246" ht="28.9" customHeight="1"/>
+    <row r="248" ht="28.9" customHeight="1"/>
+    <row r="249" ht="28.9" customHeight="1"/>
+    <row r="250" ht="28.9" customHeight="1"/>
+    <row r="251" ht="28.9" customHeight="1"/>
     <row r="255" ht="30" customHeight="1"/>
     <row r="256" ht="30" customHeight="1"/>
     <row r="257" ht="30" customHeight="1"/>
